--- a/DocDesign/RandomTool/CommonConfig/GameConfig/CommonLanguage.xlsx
+++ b/DocDesign/RandomTool/CommonConfig/GameConfig/CommonLanguage.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="557">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -91,7 +91,7 @@
     <t>VI</t>
   </si>
   <si>
-    <t>BD</t>
+    <t>BN</t>
   </si>
   <si>
     <t>ES</t>
@@ -595,43 +595,85 @@
     <t>common_block_5001</t>
   </si>
   <si>
-    <t>账号异常，目前无法参与游戏，请联系客服团队。</t>
-  </si>
-  <si>
-    <t>Account anomaly, unable to participate in the game currently, please contact the CS team</t>
-  </si>
-  <si>
-    <t>الحساب غير طبيعي، لا يمكن الانضمام إلى اللعبة حاليا، يرجى الاتصال بخدمة العملاء`</t>
-  </si>
-  <si>
-    <t>Tài khoản gặp sự cố, hiện không thể tham gia trò chơi, vui lòng liên hệ với đội ngũ hỗ trợ khách hàng.</t>
-  </si>
-  <si>
-    <t>অ্যাকাউন্টে অসঙ্গতির কারণে বর্তমানে গেমে অংশগ্রহণ করা যাচ্ছে না, অনুগ্রহ করে কাস্টমার সার্ভিস টিমের সাথে যোগাযোগ করুন।</t>
-  </si>
-  <si>
-    <t>Anomalía en la cuenta, no puedo participar en el juego actualmente, por favor contacte con el equipo de atención al cliente.</t>
-  </si>
-  <si>
-    <t>अकाउंट में गड़बड़ी है, अभी गेम में हिस्सा नहीं ले पा रहे हैं, कृपया CS टीम से संपर्क करें</t>
-  </si>
-  <si>
-    <t>Terjadi anomali pada akun, saat ini tidak dapat berpartisipasi dalam permainan, silakan hubungi tim layanan pelanggan.</t>
-  </si>
-  <si>
-    <t>Anomalia na conta, impossibilitada de participar no jogo no momento. Entre em contacto com a equipa de suporte.</t>
-  </si>
-  <si>
-    <t>เกิดความผิดปกติของบัญชี ไม่สามารถเข้าร่วมเล่นเกมได้ในขณะนี้ โปรดติดต่อทีมบริการลูกค้า</t>
-  </si>
-  <si>
-    <t>Hesap anormalliği nedeniyle şu anda oyuna katılamıyorum, lütfen müşteri hizmetleri ekibiyle iletişime geçin.</t>
-  </si>
-  <si>
-    <t>اکاؤنٹ میں بے ضابطگی، فی الحال گیم میں حصہ لینے سے قاصر، براہ کرم CS ٹیم سے رابطہ کریں۔</t>
-  </si>
-  <si>
-    <t>Anomalya sa account, hindi makasali sa laro sa kasalukuyan, mangyaring makipag-ugnayan sa CS team</t>
+    <t>此账号无法参与本次游戏。</t>
+  </si>
+  <si>
+    <t>This account cannot participate in this game.</t>
+  </si>
+  <si>
+    <t>لا يمكن لهذا الحساب المشاركة في هذه اللعبة.</t>
+  </si>
+  <si>
+    <t>Tài khoản này không thể tham gia trò chơi này.</t>
+  </si>
+  <si>
+    <t>এই অ্যাকাউন্টটি এই গেমে অংশ নিতে পারবে না।</t>
+  </si>
+  <si>
+    <t>Esta cuenta no puede participar en este juego.</t>
+  </si>
+  <si>
+    <t>यह खाता इस गेम में भाग नहीं ले सकता।</t>
+  </si>
+  <si>
+    <t>Akun ini tidak dapat berpartisipasi dalam permainan ini.</t>
+  </si>
+  <si>
+    <t>Esta conta não pode participar deste jogo.</t>
+  </si>
+  <si>
+    <t>บัญชีนี้ไม่สามารถเข้าร่วมเกมนี้ได้</t>
+  </si>
+  <si>
+    <t>Bu hesap bu oyuna katılamaz.</t>
+  </si>
+  <si>
+    <t>یہ اکاؤنٹ اس گیم میں شامل نہیں ہو سکتا۔</t>
+  </si>
+  <si>
+    <t>Hindi makakalahok ang account na ito sa larong ito.</t>
+  </si>
+  <si>
+    <t>common_block_24</t>
+  </si>
+  <si>
+    <t>币种暂时冻结，请联系官方运营部门。</t>
+  </si>
+  <si>
+    <t>Coins are temporarily frozen, please contact official operations.</t>
+  </si>
+  <si>
+    <t>العملات مجمدة مؤقتًا، يرجى التواصل مع فريق التشغيل الرسمي.</t>
+  </si>
+  <si>
+    <t>Xu đang tạm thời bị khóa, vui lòng liên hệ bộ phận vận hành chính thức.</t>
+  </si>
+  <si>
+    <t>কয়েন সাময়িকভাবে স্থগিত করা হয়েছে, অনুগ্রহ করে অফিসিয়াল অপারেশন টিমের সাথে যোগাযোগ করুন।</t>
+  </si>
+  <si>
+    <t>Las monedas están congeladas temporalmente, por favor contacta con el equipo de operaciones oficial.</t>
+  </si>
+  <si>
+    <t>सिक्के अस्थायी रूप से फ़्रीज़ हैं, कृपया आधिकारिक ऑपरेशन टीम से संपर्क करें।</t>
+  </si>
+  <si>
+    <t>Koin sementara dibekukan, silakan hubungi tim operasional resmi.</t>
+  </si>
+  <si>
+    <t>As moedas estão temporariamente congeladas, por favor entre em contato com a equipe de operações oficial.</t>
+  </si>
+  <si>
+    <t>เหรียญถูกระงับชั่วคราว กรุณาติดต่อทีมงานปฏิบัติการอย่างเป็นทางการ</t>
+  </si>
+  <si>
+    <t>Paralar geçici olarak donduruldu, lütfen resmi operasyon ekibiyle iletişime geçin.</t>
+  </si>
+  <si>
+    <t>سکے عارضی طور پر منجمد ہیں، براہ کرم آفیشل آپریشنز ٹیم سے رابطہ کریں۔</t>
+  </si>
+  <si>
+    <t>Pansamantalang na-freeze ang mga coin, mangyaring makipag-ugnayan sa opisyal na operations team.</t>
   </si>
   <si>
     <t>common_bet_error</t>
@@ -1460,6 +1502,87 @@
     <t>Error code {0}. Pakisubukang muli o makipag-ugnayan sa customer service.</t>
   </si>
   <si>
+    <t>common_activity1_rule</t>
+  </si>
+  <si>
+    <t>1. 这是幸运宝箱。如果您在某一轮游戏中没有获胜，您的一部分奖金将转入幸运宝箱并存放于其中。
+2. 当幸运宝箱内的奖金达到一定数额时，如果您在下一轮游戏中获胜，幸运宝箱可能会被激活。
+3. 幸运奖池的金额为您当轮游戏奖金的2到5倍，具体倍数随机确定。
+4. 例如：如果您在一轮游戏中赢得10,000，并且5倍倍数被激活，您将获得总计50,000的奖金。</t>
+  </si>
+  <si>
+    <t>1. This is a Lucky Chest. If you don't win a round, a portion of your winnings will be transferred to and stored in the Lucky Chest.
+2. When the winnings in the Lucky Chest reach a certain amount, the Lucky Chest may be activated if you win the next round.
+3. The Lucky Prize Pool is 2 to 5 times your winnings for that round, with the exact multiplier determined randomly.
+4. For example: If you win 10,000 in a round and the 5x multiplier is activated, you will receive a total prize of 50,000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> هذا هو صندوق الحظ، عند عدم الفوز في الجولة، سيتم تحويل جزء من الحظ إلى صندوق 1.الحظ وتخزينه فيه.
+2. عند وصول قيمة الحظ إلى حد معين، قد يتم تفعيل الصندوق في إحدى الجولات القادمة التي تحقق فيها الفوز
+3. تتراوح قيمة الجائزة الكبرى المحظوظة بين ضعفين إلى 5 أضعاف مبلغ الفوز في تلك الجولة، ويتم تحديد المضاعف بشكل عشوائي.
+4. مثال: إذا ربحت 10 الف في إحدى الجولات، وتم تفعيل 5 أضعاف، فستحصل على إجمالي 50 الف من الأرباح </t>
+  </si>
+  <si>
+    <t>1. Đây là Rương May Mắn. Nếu bạn không thắng trong một vòng chơi, một phần tiền thưởng của bạn sẽ được chuyển vào và lưu giữ trong Rương May Mắn.
+2. Khi tiền thưởng trong Rương May Mắn đạt đến một mức nhất định, Rương May Mắn có thể được kích hoạt nếu bạn thắng ở vòng chơi tiếp theo.
+3. Quỹ Giải Thưởng May Mắn bằng 2 đến 5 lần tiền thưởng của bạn trong vòng chơi đó, hệ số nhân cụ thể được xác định ngẫu nhiên.
+4. Ví dụ: Nếu bạn thắng 10.000 trong một vòng và hệ số nhân 5x được kích hoạt, bạn sẽ nhận được tổng giải thưởng là 50.000.</t>
+  </si>
+  <si>
+    <t>1. এটি একটি লাকি চেস্ট। আপনি যদি কোনো রাউন্ডে না জিতেন, তাহলে আপনার জেতার অংশের কিছু অংশ লাকি চেস্টে স্থানান্তরিত হয়ে জমা থাকবে।
+2. যখন লাকি চেস্টের জেতার পরিমাণ একটি নির্দিষ্ট পরিমাণে পৌঁছায়, তখন আপনি পরবর্তী রাউন্ডে জিতলে লাকি চেস্টটি সক্রিয় হতে পারে।
+3. লাকি পুরস্কার পুল আপনার সেই রাউন্ডের জেতার পরিমাণের 2 থেকে 5 গুণ, সঠিক গুণকটি এলোমেলোভাবে নির্ধারিত হয়।
+4. উদাহরণ: আপনি যদি একটি রাউন্ডে 10,000 জিতেন এবং 5x গুণক সক্রিয় হয়, তাহলে আপনি মোট 50,000 পুরস্কার পাবেন।</t>
+  </si>
+  <si>
+    <t>1. Este es el Cofre de la Suerte. Si no ganas en una ronda, una parte de tus ganancias se transferirá y se almacenará en el Cofre de la Suerte.
+2. Cuando las ganancias del Cofre de la Suerte alcancen cierta cantidad, el Cofre de la Suerte podrá activarse si ganas la siguiente ronda.
+3. El Fondo de Premios de la Suerte equivale a entre 2 y 5 veces tus ganancias de esa ronda, con el multiplicador exacto determinado al azar.
+4. Por ejemplo: si ganas 10.000 en una ronda y se activa el multiplicador 5x, recibirás un premio total de 50.000.</t>
+  </si>
+  <si>
+    <t>1. यह एक लकी चेस्ट है। यदि आप किसी राउंड में नहीं जीतते हैं, तो आपकी जीत का एक हिस्सा लकी चेस्ट में स्थानांतरित करके संग्रहीत कर दिया जाएगा।
+2. जब लकी चेस्ट में जीत की राशि एक निश्चित राशि तक पहुँच जाती है, तो अगले राउंड में जीतने पर लकी चेस्ट सक्रिय हो सकता है।
+3. लकी पुरस्कार पूल उस राउंड में आपकी जीत का 2 से 5 गुना होता है, सटीक गुणक यादृच्छिक रूप से निर्धारित किया जाता है।
+4. उदाहरण: यदि आप एक राउंड में 10,000 जीतते हैं और 5x गुणक सक्रिय होता है, तो आपको कुल 50,000 का पुरस्कार मिलेगा।</t>
+  </si>
+  <si>
+    <t>1. Ini adalah Peti Keberuntungan. Jika Anda tidak menang dalam satu putaran, sebagian kemenangan Anda akan dipindahkan dan disimpan di dalam Peti Keberuntungan.
+2. Ketika kemenangan di dalam Peti Keberuntungan mencapai jumlah tertentu, Peti Keberuntungan dapat diaktifkan jika Anda menang di putaran berikutnya.
+3. Kumpulan Hadiah Keberuntungan adalah 2 hingga 5 kali lipat kemenangan Anda pada putaran tersebut, dengan pengali pasti ditentukan secara acak.
+4. Contoh: Jika Anda menang 10.000 dalam satu putaran dan pengali 5x diaktifkan, Anda akan menerima total hadiah 50.000.</t>
+  </si>
+  <si>
+    <t>1. Este é o Baú da Sorte. Se você não vencer em uma rodada, uma parte dos seus ganhos será transferida e armazenada no Baú da Sorte.
+2. Quando os ganhos no Baú da Sorte atingirem um determinado valor, o Baú da Sorte poderá ser ativado se você vencer a próxima rodada.
+3. O Poço de Prêmios da Sorte equivale a 2 a 5 vezes os seus ganhos nessa rodada, com o multiplicador exato determinado aleatoriamente.
+4. Por exemplo: se você ganhar 10.000 em uma rodada e o multiplicador 5x for ativado, você receberá um prêmio total de 50.000.</t>
+  </si>
+  <si>
+    <t>1. นี่คือกล่องนำโชค หากคุณไม่ชนะในรอบนั้น เงินรางวัลส่วนหนึ่งของคุณจะถูกโอนเข้าไปเก็บไว้ในกล่องนำโชค
+2. เมื่อเงินรางวัลในกล่องนำโชคถึงจำนวนหนึ่ง กล่องนำโชคอาจถูกเปิดใช้งานหากคุณชนะในรอบถัดไป
+3. กองรางวัลนำโชคคือ 2 ถึง 5 เท่าของเงินรางวัลของคุณในรอบนั้น โดยตัวคูณที่แน่นอนจะถูกกำหนดแบบสุ่ม
+4. ตัวอย่าง: หากคุณชนะ 10,000 ในหนึ่งรอบและตัวคูณ 5x ถูกเปิดใช้งาน คุณจะได้รับรางวัลรวม 50,000</t>
+  </si>
+  <si>
+    <t>1. Bu bir Şans Sandığıdır. Bir turda kazanamazsanız, kazancınızın bir kısmı Şans Sandığına aktarılır ve orada saklanır.
+2. Şans Sandığındaki kazançlar belirli bir miktara ulaştığında, bir sonraki turda kazanırsanız Şans Sandığı etkinleştirilebilir.
+3. Şans Ödül Havuzu, o turdaki kazancınızın 2 ila 5 katıdır; kesin çarpan rastgele belirlenir.
+4. Örnek: Bir turda 10.000 kazanırsanız ve 5x çarpanı etkinleştirilirse, toplam 50.000 ödül alırsınız.</t>
+  </si>
+  <si>
+    <t>1. یہ ایک لکی چیسٹ ہے۔ اگر آپ کسی راؤنڈ میں نہیں جیتتے ہیں، تو آپ کی جیت کا ایک حصہ لکی چیسٹ میں منتقل کر کے محفوظ کر لیا جائے گا۔
+2. جب لکی چیسٹ میں جیت کی رقم ایک خاص حد تک پہنچ جائے تو اگر آپ اگلے راؤنڈ میں جیتتے ہیں تو لکی چیسٹ فعال ہو سکتی ہے۔
+3. لکی انعام پول اس راؤنڈ میں آپ کی جیت کا 2 سے 5 گنا ہوتا ہے، اور صحیح ضرب تصادفی طور پر طے کی جاتی ہے۔
+4. مثال: اگر آپ ایک راؤنڈ میں 10,000 جیتتے ہیں اور 5x ضرب فعال ہوتی ہے، تو آپ کو کل 50,000 انعام ملے گا۔</t>
+  </si>
+  <si>
+    <t>1. Ito ang Kahon ng Suwerte. Kung hindi ka manalo sa isang round, ang bahagi ng iyong panalo ay ililipat at itatago sa Kahon ng Suwerte.
+2. Kapag umabot sa isang tiyak na halaga ang mga panalo sa Kahon ng Suwerte, maaaring ma-activate ang Kahon ng Suwerte kung mananalo ka sa susunod na round.
+3. Ang Pondo ng Premyong Suwerte ay 2 hanggang 5 beses ng iyong panalo sa round na iyon, na ang eksaktong multiplier ay random na tinutukoy.
+4. Halimbawa: Kung manalo ka ng 10,000 sa isang round at ma-activate ang 5x multiplier, makakatanggap ka ng kabuuang premyo na 50,000.</t>
+  </si>
+  <si>
     <t>common_game_name_1</t>
   </si>
   <si>
@@ -1484,6 +1607,9 @@
     <t>common_game_name_7</t>
   </si>
   <si>
+    <t>YummySlot</t>
+  </si>
+  <si>
     <t>common_game_name_8</t>
   </si>
   <si>
@@ -1778,7 +1904,7 @@
     <t>common_game_name_63</t>
   </si>
   <si>
-    <t>YummySlot</t>
+    <t>RoyalTeenPatti</t>
   </si>
 </sst>
 </file>
@@ -1791,7 +1917,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1804,6 +1930,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1960,7 +2092,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.6"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2298,147 +2430,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2454,50 +2583,50 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2810,728 +2939,728 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="28.1333333333333" style="5" customWidth="1"/>
-    <col min="2" max="2" width="44.75" style="6" customWidth="1"/>
-    <col min="3" max="3" width="46.5583333333333" style="6" customWidth="1"/>
-    <col min="4" max="4" width="32.1083333333333" style="6" customWidth="1"/>
-    <col min="5" max="14" width="46.5583333333333" style="6" customWidth="1"/>
+    <col min="1" max="1" width="28.1333333333333" style="4" customWidth="1"/>
+    <col min="2" max="2" width="44.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="46.5583333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="32.1083333333333" style="5" customWidth="1"/>
+    <col min="5" max="14" width="46.5583333333333" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N8" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:14">
+      <c r="A9" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:14">
+      <c r="A10" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.5" customHeight="1" spans="1:14">
-      <c r="A11" s="11" t="s">
+    <row r="11" ht="43.5" customHeight="1" spans="1:14">
+      <c r="A11" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="N11" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="46.5" customHeight="1" spans="1:14">
-      <c r="A12" s="9" t="s">
+    <row r="12" ht="46.5" customHeight="1" spans="1:14">
+      <c r="A12" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="M12" s="14" t="s">
+      <c r="M12" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="14" t="s">
+      <c r="N12" s="13" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="56" customHeight="1" spans="1:14">
-      <c r="A13" s="11" t="s">
+    <row r="13" ht="56" customHeight="1" spans="1:14">
+      <c r="A13" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="13" t="s">
+      <c r="M13" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="12" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="49.5" customHeight="1" spans="1:14">
-      <c r="A14" s="15" t="s">
+    <row r="14" s="1" customFormat="1" ht="49.5" customHeight="1" spans="1:14">
+      <c r="A14" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="N14" s="14" t="s">
+      <c r="N14" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="45" spans="1:14">
-      <c r="A15" s="15" t="s">
+    <row r="15" s="1" customFormat="1" ht="45" customHeight="1" spans="1:14">
+      <c r="A15" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="N15" s="14" t="s">
+      <c r="N15" s="13" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="49.5" spans="1:14">
-      <c r="A16" s="15" t="s">
+    <row r="16" s="1" customFormat="1" ht="49.5" customHeight="1" spans="1:14">
+      <c r="A16" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="M16" s="14" t="s">
+      <c r="M16" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="N16" s="14" t="s">
+      <c r="N16" s="13" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" ht="40.5" spans="1:15">
-      <c r="A17" s="16" t="s">
+    <row r="17" s="2" customFormat="1" ht="40.5" customHeight="1" spans="1:15">
+      <c r="A17" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>186</v>
       </c>
       <c r="D17" s="17" t="s">
@@ -3568,364 +3697,363 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="18" t="s">
+    <row r="18" s="1" customFormat="1" ht="40.5" customHeight="1" spans="1:15">
+      <c r="A18" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="I18" s="19" t="s">
+      <c r="I18" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="J18" s="19" t="s">
+      <c r="J18" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="L18" s="19" t="s">
+      <c r="L18" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="M18" s="19" t="s">
+      <c r="M18" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="N18" s="19" t="s">
+      <c r="N18" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="O18" s="20"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="I19" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="J19" s="19" t="s">
+      <c r="J19" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K19" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M19" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="N19" s="19" t="s">
+      <c r="N19" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="O19" s="20"/>
+      <c r="O19" s="18"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I20" s="19" t="s">
+      <c r="I20" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J20" s="19" t="s">
+      <c r="J20" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="N20" s="19" t="s">
+      <c r="N20" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="O20" s="20"/>
+      <c r="O20" s="18"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="I21" s="19" t="s">
+      <c r="I21" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="K21" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="L21" s="19" t="s">
+      <c r="L21" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="N21" s="19" t="s">
+      <c r="N21" s="9" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="22" s="3" customFormat="1" ht="56.25" customHeight="1" spans="1:15">
-      <c r="A22" s="16" t="s">
+      <c r="O21" s="18"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="K22" s="17" t="s">
+      <c r="K22" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="L22" s="17" t="s">
+      <c r="L22" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="M22" s="17" t="s">
+      <c r="M22" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N22" s="9" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="18" t="s">
+    <row r="23" s="1" customFormat="1" ht="56.25" customHeight="1" spans="1:15">
+      <c r="A23" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="I23" s="19" t="s">
+      <c r="I23" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="J23" s="19" t="s">
+      <c r="J23" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="K23" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="M23" s="19" t="s">
+      <c r="M23" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="N23" s="19" t="s">
+      <c r="N23" s="13" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="I24" s="19" t="s">
+      <c r="I24" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="J24" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="L24" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="M24" s="19" t="s">
+      <c r="L24" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="N24" s="19" t="s">
+      <c r="M24" s="9" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="25" ht="202" customHeight="1" spans="1:15">
-      <c r="A25" s="21" t="s">
+      <c r="N24" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="B25" s="22" t="s">
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="B25" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="C25" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="D25" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="E25" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="F25" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="G25" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="I25" s="22" t="s">
+      <c r="H25" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="I25" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="K25" s="22" t="s">
+      <c r="J25" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="L25" s="22" t="s">
+      <c r="K25" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="M25" s="22" t="s">
+      <c r="L25" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="M25" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="N25" s="22" t="s">
+      <c r="N25" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="O25" s="20"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="18" t="s">
+    </row>
+    <row r="26" ht="202" customHeight="1" spans="1:15">
+      <c r="A26" s="10" t="s">
         <v>309</v>
       </c>
       <c r="B26" s="19" t="s">
@@ -3967,273 +4095,274 @@
       <c r="N26" s="19" t="s">
         <v>322</v>
       </c>
+      <c r="O26" s="18"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="J27" s="19" t="s">
+      <c r="J27" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="K27" s="19" t="s">
+      <c r="K27" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="M27" s="19" t="s">
+      <c r="M27" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="N27" s="19" t="s">
+      <c r="N27" s="9" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="J28" s="19" t="s">
+      <c r="J28" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="K28" s="19" t="s">
+      <c r="K28" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="L28" s="19" t="s">
+      <c r="L28" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="M28" s="19" t="s">
+      <c r="M28" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="N28" s="19" t="s">
+      <c r="N28" s="9" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I29" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="J29" s="19" t="s">
+      <c r="J29" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="K29" s="19" t="s">
+      <c r="K29" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="L29" s="19" t="s">
+      <c r="L29" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="M29" s="19" t="s">
+      <c r="M29" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="N29" s="19" t="s">
+      <c r="N29" s="9" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="I30" s="19" t="s">
+      <c r="I30" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="J30" s="19" t="s">
+      <c r="J30" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="K30" s="19" t="s">
+      <c r="K30" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="L30" s="19" t="s">
+      <c r="L30" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="M30" s="19" t="s">
+      <c r="M30" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="N30" s="19" t="s">
+      <c r="N30" s="9" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="31" s="4" customFormat="1" ht="168" customHeight="1" spans="1:15">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:15">
+      <c r="A31" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="J31" s="22" t="s">
+      <c r="J31" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="K31" s="22" t="s">
+      <c r="K31" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="L31" s="22" t="s">
+      <c r="L31" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="M31" s="23" t="s">
+      <c r="M31" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="N31" s="22" t="s">
+      <c r="N31" s="9" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="32" s="4" customFormat="1" ht="115" customHeight="1" spans="1:15">
-      <c r="A32" s="16" t="s">
+    <row r="32" s="3" customFormat="1" ht="168" customHeight="1" spans="1:15">
+      <c r="A32" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="19" t="s">
         <v>400</v>
       </c>
-      <c r="I32" s="22" t="s">
+      <c r="I32" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="J32" s="22" t="s">
+      <c r="J32" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="K32" s="22" t="s">
+      <c r="K32" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="L32" s="22" t="s">
+      <c r="L32" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="M32" s="23" t="s">
+      <c r="M32" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="N32" s="22" t="s">
+      <c r="N32" s="19" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="18" t="s">
+    <row r="33" s="3" customFormat="1" ht="115" customHeight="1" spans="1:14">
+      <c r="A33" s="14" t="s">
         <v>407</v>
       </c>
       <c r="B33" s="19" t="s">
@@ -4242,22 +4371,22 @@
       <c r="C33" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="20" t="s">
         <v>410</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="19" t="s">
         <v>415</v>
       </c>
       <c r="J33" s="19" t="s">
@@ -4269,7 +4398,7 @@
       <c r="L33" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="M33" s="19" t="s">
+      <c r="M33" s="20" t="s">
         <v>419</v>
       </c>
       <c r="N33" s="19" t="s">
@@ -4277,2484 +4406,2588 @@
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="L34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="M34" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="N34" s="19" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="18" t="s">
+      <c r="C34" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
+      <c r="D34" t="s">
+        <v>424</v>
+      </c>
+      <c r="E34" t="s">
+        <v>425</v>
+      </c>
+      <c r="F34" t="s">
+        <v>426</v>
+      </c>
+      <c r="G34" t="s">
+        <v>427</v>
+      </c>
+      <c r="H34" t="s">
+        <v>428</v>
+      </c>
+      <c r="I34" t="s">
+        <v>429</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="35" ht="202.5" customHeight="1" spans="1:14">
+      <c r="A35" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="N35" s="13" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
+      <c r="A36" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
+      <c r="A37" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
+      <c r="A38" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="18" t="s">
-        <v>427</v>
-      </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
+      <c r="A39" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
+      <c r="A40" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
+      <c r="A41" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
+      <c r="A42" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="M42" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
+      <c r="A43" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="I44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="J44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="K44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="L44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="M44" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="N44" s="19" t="s">
-        <v>433</v>
-      </c>
+      <c r="A44" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="18" t="s">
-        <v>434</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="I45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="J45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="K45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="L45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="M45" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="N45" s="19" t="s">
-        <v>435</v>
-      </c>
+      <c r="A45" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="I46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="K46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="L46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="M46" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="N46" s="19" t="s">
-        <v>437</v>
+      <c r="A46" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="N46" s="9" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="18" t="s">
-        <v>438</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="I47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="J47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="K47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="L47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="M47" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="N47" s="19" t="s">
-        <v>439</v>
+      <c r="A47" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="I48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="K48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="L48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="M48" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="N48" s="19" t="s">
-        <v>441</v>
+      <c r="A48" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="18" t="s">
-        <v>442</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="D49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="I49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="K49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="L49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="M49" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="N49" s="19" t="s">
-        <v>443</v>
+      <c r="A49" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="18" t="s">
-        <v>444</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="H50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="I50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="K50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="L50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="M50" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="N50" s="19" t="s">
-        <v>445</v>
+      <c r="A50" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="N50" s="9" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="H51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="I51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="K51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="L51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="M51" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="N51" s="19" t="s">
-        <v>447</v>
+      <c r="A51" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="18" t="s">
-        <v>448</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="H52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="I52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="J52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="K52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="L52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="M52" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="N52" s="19" t="s">
-        <v>449</v>
+      <c r="A52" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="L52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="M52" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="N52" s="9" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="G53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="I53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="J53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="K53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="L53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="M53" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="N53" s="19" t="s">
-        <v>451</v>
+      <c r="A53" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="18" t="s">
-        <v>452</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="H54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="I54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="J54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="K54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="L54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="M54" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="N54" s="19" t="s">
-        <v>453</v>
+      <c r="A54" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="M54" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="N54" s="9" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="I55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="J55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="K55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="L55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="M55" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="N55" s="19" t="s">
-        <v>455</v>
+      <c r="A55" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="I56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="J56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="L56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="M56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="N56" s="19" t="s">
-        <v>457</v>
+      <c r="A56" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="G57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="H57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="I57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="J57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="K57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="L57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="M57" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="N57" s="19" t="s">
-        <v>459</v>
+      <c r="A57" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="18" t="s">
-        <v>460</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="G58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="H58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="I58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="J58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="K58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="L58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="M58" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="N58" s="19" t="s">
-        <v>461</v>
+      <c r="A58" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="M58" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="I59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="J59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="K59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="L59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="M59" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="N59" s="19" t="s">
-        <v>463</v>
+      <c r="A59" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="N59" s="9" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19"/>
+      <c r="A60" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="M60" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="N60" s="9" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="H61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="I61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="J61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="K61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="L61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="M61" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="N61" s="19" t="s">
-        <v>466</v>
+      <c r="A61" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="G62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="I62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="J62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="K62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="L62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="M62" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="N62" s="19" t="s">
-        <v>468</v>
-      </c>
+      <c r="A62" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="18" t="s">
-        <v>469</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="H63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="I63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="J63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="K63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="L63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="M63" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="N63" s="19" t="s">
-        <v>470</v>
+      <c r="A63" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="G64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="H64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="I64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="J64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="K64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="L64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="M64" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="N64" s="19" t="s">
-        <v>472</v>
+      <c r="A64" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="L64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="I65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="J65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="K65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="L65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="M65" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="N65" s="19" t="s">
-        <v>474</v>
+      <c r="A65" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="G66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="H66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="I66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="J66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="K66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="L66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="M66" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="N66" s="19" t="s">
-        <v>476</v>
+      <c r="A66" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="L66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="B67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="H67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="I67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="J67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="K67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="L67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="M67" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="N67" s="19" t="s">
-        <v>478</v>
+      <c r="A67" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="F68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="H68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="I68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="J68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="K68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="L68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="M68" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="N68" s="19" t="s">
-        <v>480</v>
+      <c r="A68" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="H69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="I69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="J69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="K69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="L69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="M69" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="N69" s="19" t="s">
-        <v>482</v>
+      <c r="A69" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="K69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="D70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="G70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="H70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="I70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="J70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="K70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="L70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="M70" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="N70" s="19" t="s">
-        <v>484</v>
+      <c r="A70" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="N70" s="9" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="H71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="I71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="J71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="K71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="L71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="M71" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="N71" s="19" t="s">
-        <v>486</v>
+      <c r="A71" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="18" t="s">
-        <v>487</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="H72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="I72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="J72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="K72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="L72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="M72" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="N72" s="19" t="s">
-        <v>488</v>
+      <c r="A72" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="L72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="M72" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="D73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="G73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="H73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="I73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="J73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="K73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="L73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="M73" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="N73" s="19" t="s">
-        <v>490</v>
+      <c r="A73" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="G74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="H74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="I74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="J74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="K74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="L74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="M74" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="N74" s="19" t="s">
-        <v>492</v>
+      <c r="A74" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="K74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="L74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="M74" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="N74" s="9" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="18" t="s">
-        <v>493</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="F75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="G75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="H75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="I75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="J75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="K75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="L75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="M75" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="N75" s="19" t="s">
-        <v>494</v>
+      <c r="A75" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="18" t="s">
-        <v>495</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="G76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="H76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="I76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="J76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="K76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="L76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="M76" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="N76" s="19" t="s">
-        <v>496</v>
+      <c r="A76" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="K76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="L76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="M76" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="18" t="s">
-        <v>497</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="I77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="J77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="K77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="L77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="M77" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="N77" s="19" t="s">
-        <v>498</v>
+      <c r="A77" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="K77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
-      <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
-      <c r="M78" s="19"/>
-      <c r="N78" s="19"/>
+      <c r="A78" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="M78" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="18" t="s">
-        <v>500</v>
-      </c>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="19"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="19"/>
-      <c r="L79" s="19"/>
-      <c r="M79" s="19"/>
-      <c r="N79" s="19"/>
+      <c r="A79" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="18" t="s">
-        <v>501</v>
-      </c>
-      <c r="B80" s="19"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
-      <c r="K80" s="19"/>
-      <c r="L80" s="19"/>
-      <c r="M80" s="19"/>
-      <c r="N80" s="19"/>
+      <c r="A80" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
+      <c r="M80" s="9"/>
+      <c r="N80" s="9"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="F81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="G81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="H81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="I81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="J81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="K81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="L81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="M81" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="N81" s="19" t="s">
-        <v>503</v>
-      </c>
+      <c r="A81" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="9"/>
+      <c r="M81" s="9"/>
+      <c r="N81" s="9"/>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="E82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="F82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="G82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="H82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="I82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="J82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="K82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="L82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="M82" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="N82" s="19" t="s">
-        <v>505</v>
-      </c>
+      <c r="A82" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+      <c r="M82" s="9"/>
+      <c r="N82" s="9"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="19"/>
-      <c r="K83" s="19"/>
-      <c r="L83" s="19"/>
-      <c r="M83" s="19"/>
-      <c r="N83" s="19"/>
+      <c r="A83" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="K83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="M83" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="18" t="s">
-        <v>507</v>
-      </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="19"/>
-      <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19"/>
+      <c r="A84" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="K84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="L84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="M84" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="N84" s="9" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="18" t="s">
-        <v>508</v>
-      </c>
-      <c r="B85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="D85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="F85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="G85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="H85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="I85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="J85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="K85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="L85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="M85" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="N85" s="19" t="s">
-        <v>509</v>
-      </c>
+      <c r="A85" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="9"/>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="18" t="s">
-        <v>510</v>
-      </c>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="19"/>
-      <c r="K86" s="19"/>
-      <c r="L86" s="19"/>
-      <c r="M86" s="19"/>
-      <c r="N86" s="19"/>
+      <c r="A86" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="9"/>
+      <c r="M86" s="9"/>
+      <c r="N86" s="9"/>
     </row>
     <row r="87" spans="1:14">
-      <c r="A87" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19"/>
-      <c r="I87" s="19"/>
-      <c r="J87" s="19"/>
-      <c r="K87" s="19"/>
-      <c r="L87" s="19"/>
-      <c r="M87" s="19"/>
-      <c r="N87" s="19"/>
+      <c r="A87" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="K87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="M87" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="N87" s="9" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="D88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="F88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="G88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="H88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="I88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="J88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="K88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="L88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="M88" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="N88" s="19" t="s">
-        <v>513</v>
-      </c>
+      <c r="A88" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="9"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="9"/>
+      <c r="M88" s="9"/>
+      <c r="N88" s="9"/>
     </row>
     <row r="89" spans="1:14">
-      <c r="A89" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="19"/>
-      <c r="H89" s="19"/>
-      <c r="I89" s="19"/>
-      <c r="J89" s="19"/>
-      <c r="K89" s="19"/>
-      <c r="L89" s="19"/>
-      <c r="M89" s="19"/>
-      <c r="N89" s="19"/>
+      <c r="A89" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
+      <c r="M89" s="9"/>
+      <c r="N89" s="9"/>
     </row>
     <row r="90" spans="1:14">
-      <c r="A90" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="B90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="D90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="F90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="G90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="H90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="I90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="J90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="K90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="L90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="M90" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="N90" s="19" t="s">
-        <v>516</v>
+      <c r="A90" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="K90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="L90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="M90" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="N90" s="9" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="91" spans="1:14">
-      <c r="A91" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="D91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="F91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="G91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="H91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="I91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="J91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="K91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="L91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="M91" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="N91" s="19" t="s">
-        <v>518</v>
-      </c>
+      <c r="A91" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+      <c r="N91" s="9"/>
     </row>
     <row r="92" spans="1:14">
-      <c r="A92" s="18" t="s">
-        <v>519</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="D92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="E92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="F92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="G92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="H92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="I92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="J92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="K92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="L92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="M92" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="N92" s="19" t="s">
-        <v>520</v>
+      <c r="A92" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="K92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="L92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="M92" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="N92" s="9" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="93" spans="1:14">
-      <c r="A93" s="18" t="s">
-        <v>521</v>
-      </c>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="19"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="19"/>
-      <c r="I93" s="19"/>
-      <c r="J93" s="19"/>
-      <c r="K93" s="19"/>
-      <c r="L93" s="19"/>
-      <c r="M93" s="19"/>
-      <c r="N93" s="19"/>
+      <c r="A93" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="N93" s="9" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="94" spans="1:14">
-      <c r="A94" s="18" t="s">
-        <v>522</v>
-      </c>
-      <c r="B94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="F94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="G94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="H94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="I94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="J94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="K94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="L94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="M94" s="19" t="s">
-        <v>523</v>
-      </c>
-      <c r="N94" s="19" t="s">
-        <v>523</v>
+      <c r="A94" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="K94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="L94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="M94" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="N94" s="9" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="95" spans="1:14">
-      <c r="A95" s="18" t="s">
-        <v>524</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="D95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="E95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="F95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="G95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="H95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="I95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="J95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="K95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="L95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="M95" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="N95" s="19" t="s">
-        <v>525</v>
-      </c>
+      <c r="A95" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9"/>
+      <c r="L95" s="9"/>
+      <c r="M95" s="9"/>
+      <c r="N95" s="9"/>
     </row>
     <row r="96" spans="1:14">
-      <c r="A96" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="D96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="E96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="F96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="G96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="H96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="I96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="J96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="K96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="L96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="M96" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="N96" s="19" t="s">
-        <v>527</v>
+      <c r="A96" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="K96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="L96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="M96" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="N96" s="9" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="97" spans="1:14">
-      <c r="A97" s="18"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="19"/>
-      <c r="K97" s="19"/>
-      <c r="L97" s="19"/>
-      <c r="M97" s="19"/>
-      <c r="N97" s="19"/>
+      <c r="A97" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="K97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="M97" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="N97" s="9" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="98" spans="1:14">
-      <c r="A98" s="18"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="19"/>
-      <c r="J98" s="19"/>
-      <c r="K98" s="19"/>
-      <c r="L98" s="19"/>
-      <c r="M98" s="19"/>
-      <c r="N98" s="19"/>
+      <c r="A98" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="K98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="L98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="M98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="N98" s="9" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="99" spans="1:14">
-      <c r="A99" s="18"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19"/>
-      <c r="H99" s="19"/>
-      <c r="I99" s="19"/>
-      <c r="J99" s="19"/>
-      <c r="K99" s="19"/>
-      <c r="L99" s="19"/>
-      <c r="M99" s="19"/>
-      <c r="N99" s="19"/>
+      <c r="A99" s="8"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9"/>
+      <c r="L99" s="9"/>
+      <c r="M99" s="9"/>
+      <c r="N99" s="9"/>
     </row>
     <row r="100" spans="1:14">
-      <c r="A100" s="18"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
-      <c r="G100" s="19"/>
-      <c r="H100" s="19"/>
-      <c r="I100" s="19"/>
-      <c r="J100" s="19"/>
-      <c r="K100" s="19"/>
-      <c r="L100" s="19"/>
-      <c r="M100" s="19"/>
-      <c r="N100" s="19"/>
+      <c r="A100" s="8"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
+      <c r="L100" s="9"/>
+      <c r="M100" s="9"/>
+      <c r="N100" s="9"/>
     </row>
     <row r="101" spans="1:14">
-      <c r="A101" s="18"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="19"/>
-      <c r="G101" s="19"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="19"/>
-      <c r="J101" s="19"/>
-      <c r="K101" s="19"/>
-      <c r="L101" s="19"/>
-      <c r="M101" s="19"/>
-      <c r="N101" s="19"/>
+      <c r="A101" s="8"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9"/>
+      <c r="L101" s="9"/>
+      <c r="M101" s="9"/>
+      <c r="N101" s="9"/>
     </row>
     <row r="102" spans="1:14">
-      <c r="A102" s="18"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-      <c r="D102" s="19"/>
-      <c r="E102" s="19"/>
-      <c r="F102" s="19"/>
-      <c r="G102" s="19"/>
-      <c r="H102" s="19"/>
-      <c r="I102" s="19"/>
-      <c r="J102" s="19"/>
-      <c r="K102" s="19"/>
-      <c r="L102" s="19"/>
-      <c r="M102" s="19"/>
-      <c r="N102" s="19"/>
+      <c r="A102" s="8"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
+      <c r="L102" s="9"/>
+      <c r="M102" s="9"/>
+      <c r="N102" s="9"/>
     </row>
     <row r="103" spans="1:14">
-      <c r="A103" s="18"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="19"/>
-      <c r="E103" s="19"/>
-      <c r="F103" s="19"/>
-      <c r="G103" s="19"/>
-      <c r="H103" s="19"/>
-      <c r="I103" s="19"/>
-      <c r="J103" s="19"/>
-      <c r="K103" s="19"/>
-      <c r="L103" s="19"/>
-      <c r="M103" s="19"/>
-      <c r="N103" s="19"/>
+      <c r="A103" s="8"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="9"/>
+      <c r="K103" s="9"/>
+      <c r="L103" s="9"/>
+      <c r="M103" s="9"/>
+      <c r="N103" s="9"/>
     </row>
     <row r="104" spans="1:14">
-      <c r="A104" s="18"/>
-      <c r="B104" s="19"/>
-      <c r="C104" s="19"/>
-      <c r="E104" s="19"/>
-      <c r="F104" s="19"/>
-      <c r="G104" s="19"/>
-      <c r="H104" s="19"/>
-      <c r="I104" s="19"/>
-      <c r="J104" s="19"/>
-      <c r="K104" s="19"/>
-      <c r="L104" s="19"/>
-      <c r="M104" s="19"/>
-      <c r="N104" s="19"/>
+      <c r="A104" s="8"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="9"/>
+      <c r="H104" s="9"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="9"/>
+      <c r="K104" s="9"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="9"/>
+      <c r="N104" s="9"/>
     </row>
     <row r="105" spans="1:14">
-      <c r="A105" s="18"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-      <c r="E105" s="19"/>
-      <c r="F105" s="19"/>
-      <c r="G105" s="19"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="19"/>
-      <c r="J105" s="19"/>
-      <c r="K105" s="19"/>
-      <c r="L105" s="19"/>
-      <c r="M105" s="19"/>
-      <c r="N105" s="19"/>
+      <c r="A105" s="8"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="9"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="9"/>
+      <c r="K105" s="9"/>
+      <c r="L105" s="9"/>
+      <c r="M105" s="9"/>
+      <c r="N105" s="9"/>
     </row>
     <row r="106" spans="1:14">
-      <c r="A106" s="18"/>
-      <c r="B106" s="19"/>
-      <c r="C106" s="19"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="19"/>
-      <c r="H106" s="19"/>
-      <c r="I106" s="19"/>
-      <c r="J106" s="19"/>
-      <c r="K106" s="19"/>
-      <c r="L106" s="19"/>
-      <c r="M106" s="19"/>
-      <c r="N106" s="19"/>
+      <c r="A106" s="8"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="9"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="9"/>
+      <c r="M106" s="9"/>
+      <c r="N106" s="9"/>
     </row>
     <row r="107" spans="1:14">
-      <c r="A107" s="18"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-      <c r="E107" s="19"/>
-      <c r="F107" s="19"/>
-      <c r="G107" s="19"/>
-      <c r="H107" s="19"/>
-      <c r="I107" s="19"/>
-      <c r="J107" s="19"/>
-      <c r="K107" s="19"/>
-      <c r="L107" s="19"/>
-      <c r="M107" s="19"/>
-      <c r="N107" s="19"/>
+      <c r="A107" s="8"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="9"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="9"/>
+      <c r="K107" s="9"/>
+      <c r="L107" s="9"/>
+      <c r="M107" s="9"/>
+      <c r="N107" s="9"/>
     </row>
     <row r="108" spans="1:14">
-      <c r="A108" s="18"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-      <c r="E108" s="19"/>
-      <c r="F108" s="19"/>
-      <c r="G108" s="19"/>
-      <c r="H108" s="19"/>
-      <c r="I108" s="19"/>
-      <c r="J108" s="19"/>
-      <c r="K108" s="19"/>
-      <c r="L108" s="19"/>
-      <c r="M108" s="19"/>
-      <c r="N108" s="19"/>
+      <c r="A108" s="8"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9"/>
+      <c r="G108" s="9"/>
+      <c r="H108" s="9"/>
+      <c r="I108" s="9"/>
+      <c r="J108" s="9"/>
+      <c r="K108" s="9"/>
+      <c r="L108" s="9"/>
+      <c r="M108" s="9"/>
+      <c r="N108" s="9"/>
     </row>
     <row r="109" spans="1:14">
-      <c r="A109" s="18"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-      <c r="E109" s="19"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="19"/>
-      <c r="H109" s="19"/>
-      <c r="I109" s="19"/>
-      <c r="J109" s="19"/>
-      <c r="K109" s="19"/>
-      <c r="L109" s="19"/>
-      <c r="M109" s="19"/>
-      <c r="N109" s="19"/>
+      <c r="A109" s="8"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="9"/>
+      <c r="K109" s="9"/>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9"/>
+      <c r="N109" s="9"/>
+    </row>
+    <row r="110" spans="1:14">
+      <c r="A110" s="8"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="9"/>
+      <c r="K110" s="9"/>
+      <c r="L110" s="9"/>
+      <c r="M110" s="9"/>
+      <c r="N110" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
